--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q20_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009758880386672058</v>
+        <v>0.009215338865026129</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009758880386672058</v>
+        <v>0.009215338865026129</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005018649116902274</v>
+        <v>0.004977193647551714</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00918518868964098</v>
+        <v>0.008582502244861064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00918518868964098</v>
+        <v>0.008582502244861064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004664715629786382</v>
+        <v>0.004400252951367791</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0086712739301682</v>
+        <v>0.008032999814905959</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0086712739301682</v>
+        <v>0.008032999814905959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004083923747730348</v>
+        <v>0.003731239351226728</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008534897335218205</v>
+        <v>0.007897415693673837</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008534897335218205</v>
+        <v>0.007897415693673837</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00318427930509688</v>
+        <v>0.002963871739957252</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.009072967074920377</v>
+        <v>0.008446888716121084</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009072967074920377</v>
+        <v>0.008446888716121084</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002444987364613687</v>
+        <v>0.002472269848925592</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01046849529464196</v>
+        <v>0.009839787687111074</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01046849529464196</v>
+        <v>0.009839787687111074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002316887665012379</v>
+        <v>0.002492861437877804</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01300644633863669</v>
+        <v>0.01233400552141852</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01300644633863669</v>
+        <v>0.01233400552141852</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002598631469514595</v>
+        <v>0.00274583048276025</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01650817024315292</v>
+        <v>0.01574162137912875</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01650817024315292</v>
+        <v>0.01574162137912875</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003232603894960417</v>
+        <v>0.003279925161625214</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02065304954137086</v>
+        <v>0.0197279835159217</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02065304954137086</v>
+        <v>0.0197279835159217</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004805367201786239</v>
+        <v>0.004787014205413589</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02513271089579782</v>
+        <v>0.02397445786481772</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02513271089579782</v>
+        <v>0.02397445786481772</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00647254288435371</v>
+        <v>0.006396713934993589</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02945253468000227</v>
+        <v>0.0280142064293656</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02945253468000227</v>
+        <v>0.0280142064293656</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006443124426864413</v>
+        <v>0.006334929141375803</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03414283283543172</v>
+        <v>0.03239946884698809</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03414283283543172</v>
+        <v>0.03239946884698809</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005067374397299965</v>
+        <v>0.004936226177691064</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0398435528184949</v>
+        <v>0.0377926139019816</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0398435528184949</v>
+        <v>0.0377926139019816</v>
       </c>
       <c r="D14" t="n">
-        <v>0.004379467772191514</v>
+        <v>0.004185565707274017</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04627889455800376</v>
+        <v>0.04394378789835061</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04627889455800376</v>
+        <v>0.04394378789835061</v>
       </c>
       <c r="D15" t="n">
-        <v>0.005062829310408715</v>
+        <v>0.004784199608166014</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.05258510240884976</v>
+        <v>0.05000389378209559</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05258510240884976</v>
+        <v>0.05000389378209559</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00603284452731032</v>
+        <v>0.00567114152636738</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05776956058900609</v>
+        <v>0.0550009555637278</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05776956058900609</v>
+        <v>0.0550009555637278</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006799365320984091</v>
+        <v>0.006341034375521142</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06236604047191919</v>
+        <v>0.05941707265563159</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06236604047191919</v>
+        <v>0.05941707265563159</v>
       </c>
       <c r="D18" t="n">
-        <v>0.007504045234271034</v>
+        <v>0.006891249437283959</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06561965120142726</v>
+        <v>0.06253056400129334</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06561965120142726</v>
+        <v>0.06253056400129334</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008122706527804269</v>
+        <v>0.007314446267102427</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06788998937908892</v>
+        <v>0.06467326809567148</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06788998937908892</v>
+        <v>0.06467326809567148</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008682969473715288</v>
+        <v>0.007684051106936348</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.06888913130238383</v>
+        <v>0.06558009628426568</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06888913130238383</v>
+        <v>0.06558009628426568</v>
       </c>
       <c r="D21" t="n">
-        <v>0.009156651010406934</v>
+        <v>0.007913461293763847</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.06950123054568673</v>
+        <v>0.06610658195063542</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06950123054568673</v>
+        <v>0.06610658195063542</v>
       </c>
       <c r="D22" t="n">
-        <v>0.009484858614662747</v>
+        <v>0.008098595141932912</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.06866594491869159</v>
+        <v>0.06526454382058341</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06866594491869159</v>
+        <v>0.06526454382058341</v>
       </c>
       <c r="D23" t="n">
-        <v>0.009540990076626715</v>
+        <v>0.00807749328822318</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06764845343394785</v>
+        <v>0.06426432300205263</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06764845343394785</v>
+        <v>0.06426432300205263</v>
       </c>
       <c r="D24" t="n">
-        <v>0.009511983661400148</v>
+        <v>0.007921119277471808</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06621479587815335</v>
+        <v>0.06289828256439252</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06621479587815335</v>
+        <v>0.06289828256439252</v>
       </c>
       <c r="D25" t="n">
-        <v>0.009356406761441134</v>
+        <v>0.007648980368829854</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06451086412386015</v>
+        <v>0.06129389626840456</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06451086412386015</v>
+        <v>0.06129389626840456</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00913757124414516</v>
+        <v>0.007433553354709981</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.06305329182352509</v>
+        <v>0.05990891286691662</v>
       </c>
       <c r="C27" t="n">
-        <v>0.06305329182352509</v>
+        <v>0.05990891286691662</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008995392853523826</v>
+        <v>0.007290756916167168</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.060376287667307</v>
+        <v>0.05739624196042863</v>
       </c>
       <c r="C28" t="n">
-        <v>0.060376287667307</v>
+        <v>0.05739624196042863</v>
       </c>
       <c r="D28" t="n">
-        <v>0.008614433323596933</v>
+        <v>0.007139197861980768</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.05885251989723619</v>
+        <v>0.05595933421744106</v>
       </c>
       <c r="C29" t="n">
-        <v>0.05885251989723619</v>
+        <v>0.05595933421744106</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008532706259071824</v>
+        <v>0.006970231467632378</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.05831978898135544</v>
+        <v>0.05548169877034018</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05831978898135544</v>
+        <v>0.05548169877034018</v>
       </c>
       <c r="D30" t="n">
-        <v>0.008490106170038583</v>
+        <v>0.007062765781385652</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.05740527650378694</v>
+        <v>0.05462400378839573</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05740527650378694</v>
+        <v>0.05462400378839573</v>
       </c>
       <c r="D31" t="n">
-        <v>0.008518561042679909</v>
+        <v>0.007125188436957672</v>
       </c>
     </row>
   </sheetData>
